--- a/modules/warehouse/uploads/file_sample/Sample_import_commodity_file_en_1.xlsx
+++ b/modules/warehouse/uploads/file_sample/Sample_import_commodity_file_en_1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20373"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\sofware\perfex_webapp\branches\perfex_development\perfex_webapp\modules\warehouse\uploads\file_sample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD7684E-292D-4A9A-A263-ABF48ED318ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8647B5-ABBD-462D-B68D-028018A12116}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Sku Code</t>
   </si>
@@ -60,9 +60,6 @@
     <t>Unit</t>
   </si>
   <si>
-    <t>(*)Commodity Group</t>
-  </si>
-  <si>
     <t>Profit rate(%)</t>
   </si>
   <si>
@@ -148,13 +145,58 @@
   </si>
   <si>
     <t>Tax2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(*)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Item Type</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(*)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Commodity Group</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,6 +224,30 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -244,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -263,6 +329,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -545,84 +614,88 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="20" width="33.5703125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="3" customWidth="1"/>
-    <col min="22" max="23" width="22" style="3" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="21" width="33.5703125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="3" customWidth="1"/>
+    <col min="23" max="24" width="22" style="3" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="2" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:24" s="2" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="D1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="R1" s="4" t="s">
+      <c r="T1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="U1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="T1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="W1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="X1" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
